--- a/report_7.xlsx
+++ b/report_7.xlsx
@@ -9939,7 +9939,7 @@
         <v>41766</v>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4369</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -9965,7 +9965,7 @@
         <v>41861</v>
       </c>
       <c r="E3" t="n">
-        <v>4269</v>
+        <v>4274</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -9991,7 +9991,7 @@
         <v>41923</v>
       </c>
       <c r="E4" t="n">
-        <v>4207</v>
+        <v>4212</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -10017,7 +10017,7 @@
         <v>42105</v>
       </c>
       <c r="E5" t="n">
-        <v>4025</v>
+        <v>4030</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -10043,7 +10043,7 @@
         <v>42135</v>
       </c>
       <c r="E6" t="n">
-        <v>3995</v>
+        <v>4000</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -10069,7 +10069,7 @@
         <v>42160</v>
       </c>
       <c r="E7" t="n">
-        <v>3970</v>
+        <v>3975</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -10095,7 +10095,7 @@
         <v>42529</v>
       </c>
       <c r="E8" t="n">
-        <v>3601</v>
+        <v>3606</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -10121,7 +10121,7 @@
         <v>42681</v>
       </c>
       <c r="E9" t="n">
-        <v>3449</v>
+        <v>3454</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -10147,7 +10147,7 @@
         <v>42959</v>
       </c>
       <c r="E10" t="n">
-        <v>3171</v>
+        <v>3176</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -10173,7 +10173,7 @@
         <v>43137</v>
       </c>
       <c r="E11" t="n">
-        <v>2993</v>
+        <v>2998</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -10199,7 +10199,7 @@
         <v>43137</v>
       </c>
       <c r="E12" t="n">
-        <v>2993</v>
+        <v>2998</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -10225,7 +10225,7 @@
         <v>43253</v>
       </c>
       <c r="E13" t="n">
-        <v>2877</v>
+        <v>2882</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -10251,7 +10251,7 @@
         <v>43286</v>
       </c>
       <c r="E14" t="n">
-        <v>2844</v>
+        <v>2849</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -10277,7 +10277,7 @@
         <v>43316</v>
       </c>
       <c r="E15" t="n">
-        <v>2814</v>
+        <v>2819</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -10303,7 +10303,7 @@
         <v>43319</v>
       </c>
       <c r="E16" t="n">
-        <v>2811</v>
+        <v>2816</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -10329,7 +10329,7 @@
         <v>43374</v>
       </c>
       <c r="E17" t="n">
-        <v>2756</v>
+        <v>2761</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -10355,7 +10355,7 @@
         <v>43472</v>
       </c>
       <c r="E18" t="n">
-        <v>2658</v>
+        <v>2663</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -10381,7 +10381,7 @@
         <v>43651</v>
       </c>
       <c r="E19" t="n">
-        <v>2479</v>
+        <v>2484</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -10407,7 +10407,7 @@
         <v>43657</v>
       </c>
       <c r="E20" t="n">
-        <v>2473</v>
+        <v>2478</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -10433,7 +10433,7 @@
         <v>43714</v>
       </c>
       <c r="E21" t="n">
-        <v>2416</v>
+        <v>2421</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -10459,7 +10459,7 @@
         <v>43739</v>
       </c>
       <c r="E22" t="n">
-        <v>2391</v>
+        <v>2396</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -10485,7 +10485,7 @@
         <v>43741</v>
       </c>
       <c r="E23" t="n">
-        <v>2389</v>
+        <v>2394</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -10511,7 +10511,7 @@
         <v>43741</v>
       </c>
       <c r="E24" t="n">
-        <v>2389</v>
+        <v>2394</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -10537,7 +10537,7 @@
         <v>43810</v>
       </c>
       <c r="E25" t="n">
-        <v>2320</v>
+        <v>2325</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -10563,7 +10563,7 @@
         <v>43865</v>
       </c>
       <c r="E26" t="n">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -10589,7 +10589,7 @@
         <v>43932</v>
       </c>
       <c r="E27" t="n">
-        <v>2198</v>
+        <v>2203</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -10615,7 +10615,7 @@
         <v>43957</v>
       </c>
       <c r="E28" t="n">
-        <v>2173</v>
+        <v>2178</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -10641,7 +10641,7 @@
         <v>43961</v>
       </c>
       <c r="E29" t="n">
-        <v>2169</v>
+        <v>2174</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -10667,7 +10667,7 @@
         <v>43963</v>
       </c>
       <c r="E30" t="n">
-        <v>2167</v>
+        <v>2172</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -10693,7 +10693,7 @@
         <v>44055</v>
       </c>
       <c r="E31" t="n">
-        <v>2075</v>
+        <v>2080</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -10719,7 +10719,7 @@
         <v>44144</v>
       </c>
       <c r="E32" t="n">
-        <v>1986</v>
+        <v>1991</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -10745,7 +10745,7 @@
         <v>44289</v>
       </c>
       <c r="E33" t="n">
-        <v>1841</v>
+        <v>1846</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -10771,7 +10771,7 @@
         <v>44416</v>
       </c>
       <c r="E34" t="n">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -10797,7 +10797,7 @@
         <v>44418</v>
       </c>
       <c r="E35" t="n">
-        <v>1712</v>
+        <v>1717</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -10823,7 +10823,7 @@
         <v>44445</v>
       </c>
       <c r="E36" t="n">
-        <v>1685</v>
+        <v>1690</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -10849,7 +10849,7 @@
         <v>44449</v>
       </c>
       <c r="E37" t="n">
-        <v>1681</v>
+        <v>1686</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -10875,7 +10875,7 @@
         <v>44449</v>
       </c>
       <c r="E38" t="n">
-        <v>1681</v>
+        <v>1686</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -10901,7 +10901,7 @@
         <v>44479</v>
       </c>
       <c r="E39" t="n">
-        <v>1651</v>
+        <v>1656</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -10927,7 +10927,7 @@
         <v>44479</v>
       </c>
       <c r="E40" t="n">
-        <v>1651</v>
+        <v>1656</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -10953,7 +10953,7 @@
         <v>44509</v>
       </c>
       <c r="E41" t="n">
-        <v>1621</v>
+        <v>1626</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -10979,7 +10979,7 @@
         <v>44565</v>
       </c>
       <c r="E42" t="n">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -11005,7 +11005,7 @@
         <v>44596</v>
       </c>
       <c r="E43" t="n">
-        <v>1534</v>
+        <v>1539</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -11031,7 +11031,7 @@
         <v>44600</v>
       </c>
       <c r="E44" t="n">
-        <v>1530</v>
+        <v>1535</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -11057,7 +11057,7 @@
         <v>44626</v>
       </c>
       <c r="E45" t="n">
-        <v>1504</v>
+        <v>1509</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
@@ -11083,7 +11083,7 @@
         <v>44627</v>
       </c>
       <c r="E46" t="n">
-        <v>1503</v>
+        <v>1508</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
@@ -11109,7 +11109,7 @@
         <v>44632</v>
       </c>
       <c r="E47" t="n">
-        <v>1498</v>
+        <v>1503</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -11135,7 +11135,7 @@
         <v>44686</v>
       </c>
       <c r="E48" t="n">
-        <v>1444</v>
+        <v>1449</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -11161,7 +11161,7 @@
         <v>44716</v>
       </c>
       <c r="E49" t="n">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -11187,7 +11187,7 @@
         <v>44841</v>
       </c>
       <c r="E50" t="n">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
@@ -11213,7 +11213,7 @@
         <v>44876</v>
       </c>
       <c r="E51" t="n">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -11239,7 +11239,7 @@
         <v>44964</v>
       </c>
       <c r="E52" t="n">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
@@ -11265,7 +11265,7 @@
         <v>44991</v>
       </c>
       <c r="E53" t="n">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -11291,7 +11291,7 @@
         <v>45047</v>
       </c>
       <c r="E54" t="n">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -11317,7 +11317,7 @@
         <v>45052</v>
       </c>
       <c r="E55" t="n">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -11343,7 +11343,7 @@
         <v>45055</v>
       </c>
       <c r="E56" t="n">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
@@ -11369,7 +11369,7 @@
         <v>45204</v>
       </c>
       <c r="E57" t="n">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
@@ -11395,7 +11395,7 @@
         <v>45262</v>
       </c>
       <c r="E58" t="n">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
@@ -11421,7 +11421,7 @@
         <v>45269</v>
       </c>
       <c r="E59" t="n">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
@@ -11447,7 +11447,7 @@
         <v>45323</v>
       </c>
       <c r="E60" t="n">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
@@ -11473,7 +11473,7 @@
         <v>45352</v>
       </c>
       <c r="E61" t="n">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
@@ -11499,7 +11499,7 @@
         <v>45384</v>
       </c>
       <c r="E62" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -11525,7 +11525,7 @@
         <v>45391</v>
       </c>
       <c r="E63" t="n">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
@@ -11551,7 +11551,7 @@
         <v>45415</v>
       </c>
       <c r="E64" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
@@ -11577,7 +11577,7 @@
         <v>45449</v>
       </c>
       <c r="E65" t="n">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
@@ -11603,7 +11603,7 @@
         <v>45513</v>
       </c>
       <c r="E66" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
@@ -11629,7 +11629,7 @@
         <v>45516</v>
       </c>
       <c r="E67" t="n">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
@@ -11655,7 +11655,7 @@
         <v>45546</v>
       </c>
       <c r="E68" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
@@ -11681,7 +11681,7 @@
         <v>45567</v>
       </c>
       <c r="E69" t="n">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -11707,7 +11707,7 @@
         <v>45571</v>
       </c>
       <c r="E70" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
@@ -11733,7 +11733,7 @@
         <v>45608</v>
       </c>
       <c r="E71" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
@@ -11759,7 +11759,7 @@
         <v>45632</v>
       </c>
       <c r="E72" t="n">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
@@ -11785,7 +11785,7 @@
         <v>45633</v>
       </c>
       <c r="E73" t="n">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
@@ -11811,7 +11811,7 @@
         <v>45668</v>
       </c>
       <c r="E74" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -11837,7 +11837,7 @@
         <v>45727</v>
       </c>
       <c r="E75" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
@@ -11863,7 +11863,7 @@
         <v>45727</v>
       </c>
       <c r="E76" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
@@ -11889,7 +11889,7 @@
         <v>45749</v>
       </c>
       <c r="E77" t="n">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -11915,7 +11915,7 @@
         <v>45757</v>
       </c>
       <c r="E78" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -11941,7 +11941,7 @@
         <v>45779</v>
       </c>
       <c r="E79" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
@@ -11967,7 +11967,7 @@
         <v>45781</v>
       </c>
       <c r="E80" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
@@ -11993,7 +11993,7 @@
         <v>45812</v>
       </c>
       <c r="E81" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -12019,7 +12019,7 @@
         <v>45815</v>
       </c>
       <c r="E82" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         <v>45817</v>
       </c>
       <c r="E83" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F83" t="b">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>45818</v>
       </c>
       <c r="E84" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F84" t="b">
         <v>1</v>
@@ -12097,7 +12097,7 @@
         <v>45841</v>
       </c>
       <c r="E85" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F85" t="b">
         <v>0</v>
@@ -12123,7 +12123,7 @@
         <v>45875</v>
       </c>
       <c r="E86" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
@@ -12149,7 +12149,7 @@
         <v>45903</v>
       </c>
       <c r="E87" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F87" t="b">
         <v>0</v>
@@ -12175,7 +12175,7 @@
         <v>45909</v>
       </c>
       <c r="E88" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F88" t="b">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>45934</v>
       </c>
       <c r="E89" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F89" t="b">
         <v>0</v>
@@ -12227,7 +12227,7 @@
         <v>45935</v>
       </c>
       <c r="E90" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F90" t="b">
         <v>0</v>
@@ -12253,7 +12253,7 @@
         <v>45941</v>
       </c>
       <c r="E91" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F91" t="b">
         <v>0</v>
@@ -12279,7 +12279,7 @@
         <v>45966</v>
       </c>
       <c r="E92" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F92" t="b">
         <v>0</v>
@@ -12305,7 +12305,7 @@
         <v>45969</v>
       </c>
       <c r="E93" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F93" t="b">
         <v>0</v>
@@ -12331,7 +12331,7 @@
         <v>45970</v>
       </c>
       <c r="E94" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F94" t="b">
         <v>0</v>
@@ -12357,7 +12357,7 @@
         <v>45972</v>
       </c>
       <c r="E95" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F95" t="b">
         <v>0</v>
@@ -12383,7 +12383,7 @@
         <v>45992</v>
       </c>
       <c r="E96" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F96" t="b">
         <v>0</v>
@@ -12409,7 +12409,7 @@
         <v>45995</v>
       </c>
       <c r="E97" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F97" t="b">
         <v>0</v>
@@ -12435,7 +12435,7 @@
         <v>45995</v>
       </c>
       <c r="E98" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F98" t="b">
         <v>0</v>
@@ -12461,7 +12461,7 @@
         <v>46026</v>
       </c>
       <c r="E99" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F99" t="b">
         <v>0</v>
@@ -12487,7 +12487,7 @@
         <v>46056</v>
       </c>
       <c r="E100" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F100" t="b">
         <v>0</v>
@@ -12513,7 +12513,7 @@
         <v>46115</v>
       </c>
       <c r="E101" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F101" t="b">
         <v>0</v>
@@ -12539,7 +12539,7 @@
         <v>46122</v>
       </c>
       <c r="E102" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F102" t="b">
         <v>0</v>
@@ -33829,7 +33829,7 @@
         <v>46143</v>
       </c>
       <c r="E989" t="n">
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="F989" t="b">
         <v>0</v>
@@ -33855,7 +33855,7 @@
         <v>46176</v>
       </c>
       <c r="E990" t="n">
-        <v>-46</v>
+        <v>-41</v>
       </c>
       <c r="F990" t="b">
         <v>0</v>
@@ -33881,7 +33881,7 @@
         <v>46177</v>
       </c>
       <c r="E991" t="n">
-        <v>-47</v>
+        <v>-42</v>
       </c>
       <c r="F991" t="b">
         <v>0</v>
@@ -33907,7 +33907,7 @@
         <v>46177</v>
       </c>
       <c r="E992" t="n">
-        <v>-47</v>
+        <v>-42</v>
       </c>
       <c r="F992" t="b">
         <v>0</v>
@@ -33933,7 +33933,7 @@
         <v>46180</v>
       </c>
       <c r="E993" t="n">
-        <v>-50</v>
+        <v>-45</v>
       </c>
       <c r="F993" t="b">
         <v>1</v>
@@ -33959,7 +33959,7 @@
         <v>46204</v>
       </c>
       <c r="E994" t="n">
-        <v>-74</v>
+        <v>-69</v>
       </c>
       <c r="F994" t="b">
         <v>0</v>
@@ -33985,7 +33985,7 @@
         <v>46210</v>
       </c>
       <c r="E995" t="n">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="F995" t="b">
         <v>0</v>
@@ -34011,7 +34011,7 @@
         <v>46235</v>
       </c>
       <c r="E996" t="n">
-        <v>-105</v>
+        <v>-100</v>
       </c>
       <c r="F996" t="b">
         <v>0</v>
@@ -34037,7 +34037,7 @@
         <v>46296</v>
       </c>
       <c r="E997" t="n">
-        <v>-166</v>
+        <v>-161</v>
       </c>
       <c r="F997" t="b">
         <v>0</v>
@@ -34063,7 +34063,7 @@
         <v>46328</v>
       </c>
       <c r="E998" t="n">
-        <v>-198</v>
+        <v>-193</v>
       </c>
       <c r="F998" t="b">
         <v>0</v>
@@ -34089,7 +34089,7 @@
         <v>46336</v>
       </c>
       <c r="E999" t="n">
-        <v>-206</v>
+        <v>-201</v>
       </c>
       <c r="F999" t="b">
         <v>0</v>
@@ -34115,7 +34115,7 @@
         <v>46357</v>
       </c>
       <c r="E1000" t="n">
-        <v>-227</v>
+        <v>-222</v>
       </c>
       <c r="F1000" t="b">
         <v>0</v>
@@ -34141,7 +34141,7 @@
         <v>46360</v>
       </c>
       <c r="E1001" t="n">
-        <v>-230</v>
+        <v>-225</v>
       </c>
       <c r="F1001" t="b">
         <v>0</v>
@@ -34167,7 +34167,7 @@
         <v>46360</v>
       </c>
       <c r="E1002" t="n">
-        <v>-230</v>
+        <v>-225</v>
       </c>
       <c r="F1002" t="b">
         <v>0</v>
